--- a/public/templates/attendee-roster/attendee_roster_import_template_sample.xlsx
+++ b/public/templates/attendee-roster/attendee_roster_import_template_sample.xlsx
@@ -402,7 +402,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>FCOC Attendee Roster Import Template - Sample</v>
+        <v>EpicentraX Attendee Roster Import Template - Sample</v>
       </c>
       <c r="B1" t="str">
         <v/>

--- a/public/templates/attendee-roster/attendee_roster_import_template_sample.xlsx
+++ b/public/templates/attendee-roster/attendee_roster_import_template_sample.xlsx
@@ -1213,7 +1213,7 @@
         <v>boolean_yes_no</v>
       </c>
       <c r="D26" t="str">
-        <v>Whether this is the Pilot's first time at an FCOC event. Yes/Y/True/1 is Yes; anything else (including blank) is No.</v>
+        <v>Whether this is the Pilot's first time at one of your events. Yes/Y/True/1 is Yes; anything else (including blank) is No.</v>
       </c>
       <c r="E26" t="str">
         <v>No</v>
